--- a/docs/configs/Upgrades.xlsx
+++ b/docs/configs/Upgrades.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +27,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,8 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,11 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,600 +431,670 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>升级ID</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>是否炮塔卡</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>炮塔类型</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Icon</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>IsTurret</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>TurretType</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>急行军</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>移动速度+25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>boot</t>
         </is>
       </c>
-      <c r="E4" s="2" t="b">
+      <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>carry</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>军用背包</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>携带上限+5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="E5" s="2" t="b">
+      <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>atk</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>利刃强化</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>攻击力+1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>sword</t>
         </is>
       </c>
-      <c r="E6" s="2" t="b">
+      <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>atkspd</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>疾风斩</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>攻击速度+30%</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>wind</t>
         </is>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>长臂猿</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>攻击范围+35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>magnet</t>
         </is>
       </c>
-      <c r="E8" s="2" t="b">
+      <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>物资交换</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>提交金币+50%</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>coin</t>
         </is>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="F9" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>spawn</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>丰收区域</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>资源生成+30%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="E10" s="2" t="b">
+      <c r="F10" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>ore_luck</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>探矿直觉</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>矿石出现率翻倍</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>gem</t>
         </is>
       </c>
-      <c r="E11" s="2" t="b">
+      <c r="F11" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>制动系统</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>列车速度-15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>gear</t>
         </is>
       </c>
-      <c r="E12" s="2" t="b">
+      <c r="F12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>repair</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>应急维修</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>列车回复30HP</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E13" s="2" t="b">
+      <c r="F13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>装甲强化</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>列车最大HP+25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="b">
+      <c r="F14" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>multi</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>双倍搜刮</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>采集掉落概率×2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>fairy</t>
         </is>
       </c>
-      <c r="E15" s="2" t="b">
+      <c r="F15" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>turret_arrow</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>弓箭炮塔</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>解锁弓箭炮塔</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>turret_arrow</t>
         </is>
       </c>
-      <c r="E16" s="2" t="b">
+      <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>arrow</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>turret_minigun</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>机关枪塔</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>解锁机关枪炮塔</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>turret_minigun</t>
         </is>
       </c>
-      <c r="E17" s="2" t="b">
+      <c r="F17" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>minigun</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>turret_flame</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>喷火炮塔</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>解锁喷火炮塔</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>turret_flame</t>
         </is>
       </c>
-      <c r="E18" s="2" t="b">
+      <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>flame</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>turret_sniper</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>狙击炮塔</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>解锁狙击炮塔</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>turret_sniper</t>
         </is>
       </c>
-      <c r="E19" s="2" t="b">
+      <c r="F19" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>sniper</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>turret_electric</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>电能炮塔</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>解锁电能炮塔</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>turret_electric</t>
         </is>
       </c>
-      <c r="E20" s="2" t="b">
+      <c r="F20" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>electric</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>turret_rocket</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>火箭炮塔</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>解锁火箭炮塔</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>turret_rocket</t>
         </is>
       </c>
-      <c r="E21" s="2" t="b">
+      <c r="F21" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>rocket</t>
         </is>
